--- a/artfynd/A 22534-2026 artfynd.xlsx
+++ b/artfynd/A 22534-2026 artfynd.xlsx
@@ -1005,57 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133571642</v>
+        <v>133571653</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635735</v>
+        <v>635678</v>
       </c>
       <c r="R5" t="n">
-        <v>6661736</v>
+        <v>6661737</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,48 +1112,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133571653</v>
+        <v>133571642</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635678</v>
+        <v>635735</v>
       </c>
       <c r="R6" t="n">
-        <v>6661737</v>
+        <v>6661736</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 22534-2026 artfynd.xlsx
+++ b/artfynd/A 22534-2026 artfynd.xlsx
@@ -1005,48 +1005,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133571653</v>
+        <v>133571642</v>
       </c>
       <c r="B5" t="n">
-        <v>8444</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635678</v>
+        <v>635735</v>
       </c>
       <c r="R5" t="n">
-        <v>6661737</v>
+        <v>6661736</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133571642</v>
+        <v>133571663</v>
       </c>
       <c r="B6" t="n">
         <v>99130</v>
@@ -1140,11 +1149,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1156,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635735</v>
+        <v>635726</v>
       </c>
       <c r="R6" t="n">
-        <v>6661736</v>
+        <v>6661845</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,53 +1233,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133571663</v>
+        <v>133571653</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635726</v>
+        <v>635678</v>
       </c>
       <c r="R7" t="n">
-        <v>6661845</v>
+        <v>6661737</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1563,54 +1563,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133571661</v>
+        <v>133571659</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635740</v>
+        <v>635708</v>
       </c>
       <c r="R10" t="n">
-        <v>6661838</v>
+        <v>6661736</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1642,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1643,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,45 +1675,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133571659</v>
+        <v>133571661</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635708</v>
+        <v>635740</v>
       </c>
       <c r="R11" t="n">
-        <v>6661736</v>
+        <v>6661838</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1749,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,12 +1764,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,45 +1791,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133571652</v>
+        <v>133571664</v>
       </c>
       <c r="B12" t="n">
-        <v>97370</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635691</v>
+        <v>635725</v>
       </c>
       <c r="R12" t="n">
-        <v>6661724</v>
+        <v>6661853</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,54 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133571664</v>
+        <v>133571652</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>97370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635725</v>
+        <v>635691</v>
       </c>
       <c r="R13" t="n">
-        <v>6661853</v>
+        <v>6661724</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 22534-2026 artfynd.xlsx
+++ b/artfynd/A 22534-2026 artfynd.xlsx
@@ -2335,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133571655</v>
+        <v>133571660</v>
       </c>
       <c r="B17" t="n">
         <v>99181</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635723</v>
+        <v>635734</v>
       </c>
       <c r="R17" t="n">
-        <v>6661739</v>
+        <v>6661832</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133571660</v>
+        <v>133571655</v>
       </c>
       <c r="B18" t="n">
         <v>99181</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635734</v>
+        <v>635723</v>
       </c>
       <c r="R18" t="n">
-        <v>6661832</v>
+        <v>6661739</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 22534-2026 artfynd.xlsx
+++ b/artfynd/A 22534-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133571651</v>
+        <v>133571639</v>
       </c>
       <c r="B2" t="n">
-        <v>97421</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635702</v>
+        <v>635751</v>
       </c>
       <c r="R2" t="n">
-        <v>6661714</v>
+        <v>6661719</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133571666</v>
+        <v>133571646</v>
       </c>
       <c r="B3" t="n">
-        <v>99181</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635748</v>
+        <v>635743</v>
       </c>
       <c r="R3" t="n">
-        <v>6661864</v>
+        <v>6661682</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133571662</v>
+        <v>133571649</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635745</v>
+        <v>635716</v>
       </c>
       <c r="R4" t="n">
-        <v>6661840</v>
+        <v>6661648</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133571642</v>
+        <v>133571650</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635735</v>
+        <v>635698</v>
       </c>
       <c r="R5" t="n">
-        <v>6661736</v>
+        <v>6661719</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133571653</v>
+        <v>133571651</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>97435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635678</v>
+        <v>635702</v>
       </c>
       <c r="R6" t="n">
-        <v>6661737</v>
+        <v>6661714</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,50 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133571663</v>
+        <v>133571652</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>97435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635726</v>
+        <v>635691</v>
       </c>
       <c r="R7" t="n">
-        <v>6661845</v>
+        <v>6661724</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,57 +1317,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133571645</v>
+        <v>133571657</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>97435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635738</v>
+        <v>635736</v>
       </c>
       <c r="R8" t="n">
-        <v>6661687</v>
+        <v>6661758</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133571650</v>
+        <v>133571658</v>
       </c>
       <c r="B9" t="n">
-        <v>97421</v>
+        <v>97435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635698</v>
+        <v>635716</v>
       </c>
       <c r="R9" t="n">
-        <v>6661719</v>
+        <v>6661738</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,54 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133571661</v>
+        <v>133571659</v>
       </c>
       <c r="B10" t="n">
-        <v>99181</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635740</v>
+        <v>635708</v>
       </c>
       <c r="R10" t="n">
-        <v>6661838</v>
+        <v>6661736</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1642,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1611,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133571659</v>
+        <v>133571641</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>4782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635708</v>
+        <v>635733</v>
       </c>
       <c r="R11" t="n">
-        <v>6661736</v>
+        <v>6661734</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1749,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,12 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133571652</v>
+        <v>133571648</v>
       </c>
       <c r="B12" t="n">
-        <v>97421</v>
+        <v>5201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635691</v>
+        <v>635711</v>
       </c>
       <c r="R12" t="n">
-        <v>6661724</v>
+        <v>6661634</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,57 +1857,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133571664</v>
+        <v>133571653</v>
       </c>
       <c r="B13" t="n">
-        <v>99181</v>
+        <v>8449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635725</v>
+        <v>635678</v>
       </c>
       <c r="R13" t="n">
-        <v>6661853</v>
+        <v>6661737</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,48 +1964,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133571649</v>
+        <v>133571642</v>
       </c>
       <c r="B14" t="n">
-        <v>97421</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635716</v>
+        <v>635735</v>
       </c>
       <c r="R14" t="n">
-        <v>6661648</v>
+        <v>6661736</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,45 +2080,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133571641</v>
+        <v>133571643</v>
       </c>
       <c r="B15" t="n">
-        <v>4782</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635733</v>
+        <v>635734</v>
       </c>
       <c r="R15" t="n">
-        <v>6661734</v>
+        <v>6661735</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2191,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,48 +2196,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133571657</v>
+        <v>133571645</v>
       </c>
       <c r="B16" t="n">
-        <v>97421</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635736</v>
+        <v>635738</v>
       </c>
       <c r="R16" t="n">
-        <v>6661758</v>
+        <v>6661687</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2298,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,10 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133571660</v>
+        <v>133571655</v>
       </c>
       <c r="B17" t="n">
-        <v>99181</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2342,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2379,10 +2356,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635734</v>
+        <v>635723</v>
       </c>
       <c r="R17" t="n">
-        <v>6661832</v>
+        <v>6661739</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2414,7 +2391,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2424,7 +2401,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133571655</v>
+        <v>133571656</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,7 +2458,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2495,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635723</v>
+        <v>635719</v>
       </c>
       <c r="R18" t="n">
-        <v>6661739</v>
+        <v>6661738</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2530,7 +2507,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2517,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133571643</v>
+        <v>133571660</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,7 +2574,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2614,7 +2591,7 @@
         <v>635734</v>
       </c>
       <c r="R19" t="n">
-        <v>6661735</v>
+        <v>6661832</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2646,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2656,7 +2633,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,45 +2660,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133571658</v>
+        <v>133571661</v>
       </c>
       <c r="B20" t="n">
-        <v>97421</v>
+        <v>99195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635716</v>
+        <v>635740</v>
       </c>
       <c r="R20" t="n">
-        <v>6661738</v>
+        <v>6661838</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2763,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133571656</v>
+        <v>133571662</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2806,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2834,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635719</v>
+        <v>635745</v>
       </c>
       <c r="R21" t="n">
-        <v>6661738</v>
+        <v>6661840</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2869,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2879,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,48 +2892,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133571646</v>
+        <v>133571663</v>
       </c>
       <c r="B22" t="n">
-        <v>97421</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ramsjön Ost, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635743</v>
+        <v>635726</v>
       </c>
       <c r="R22" t="n">
-        <v>6661682</v>
+        <v>6661845</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2976,7 +2967,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2986,7 +2977,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,6 +3001,229 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133571664</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ramsjön Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>635725</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6661853</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133571666</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ramsjön Ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>635748</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6661864</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
